--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-18T16:53:11.414Z</t>
+    <t>2026-06-18T18:17:07.119Z</t>
   </si>
   <si>
     <t>The Trusted Payments and Data Company - Deluxe</t>
